--- a/e2e/tests/dados/planilha_faixa.xlsx
+++ b/e2e/tests/dados/planilha_faixa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,28 +609,52 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Lúcia Ferraz</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>55566677788</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>(11) 94444-7777</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Sem Código</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>44455566600</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>(11) 95555-6666</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>10,00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>16/09/2026</t>
         </is>

--- a/e2e/tests/dados/planilha_faixa.xlsx
+++ b/e2e/tests/dados/planilha_faixa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -660,6 +660,38 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Paulo Zanetti</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>66677788899</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>(11) 97777-0107</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
